--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92566430133</v>
+        <v>46157.93093088803</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93093088803</v>
+        <v>46157.93169597357</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93169597357</v>
+        <v>46157.93398312142</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93398312142</v>
+        <v>46157.93716054397</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93716054397</v>
+        <v>46158.28214656758</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28214656758</v>
+        <v>46158.29676108972</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29676108972</v>
+        <v>46158.29812766161</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29812766161</v>
+        <v>46158.3338564233</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3338564233</v>
+        <v>46158.36855398562</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/5. Колеса даром/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36855398562</v>
+        <v>46158.37286145867</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
